--- a/outputs/Summary of NPZ File Changes.xlsx
+++ b/outputs/Summary of NPZ File Changes.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meibinchen/Documents/GitHub/EEE-Model-Dashboard-Integration/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F425EE2-D1CC-CE4A-ADFA-6385CDC6C0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB8C3C0-442B-DE48-961A-A5A98EAC11A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10380" yWindow="1380" windowWidth="30980" windowHeight="24880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10380" yWindow="1380" windowWidth="30980" windowHeight="24880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="2" r:id="rId1"/>
-    <sheet name="NPZ comparison" sheetId="1" r:id="rId2"/>
+    <sheet name="NPZ comparison" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -551,19 +550,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="81.83203125" customWidth="1"/>
-    <col min="2" max="3" width="55" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -675,7 +661,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
